--- a/src/test/resources/testdata/Execution_Report.xlsx
+++ b/src/test/resources/testdata/Execution_Report.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="205">
   <si>
     <t>TestCase Name</t>
   </si>
@@ -143,6 +143,498 @@
   </si>
   <si>
     <t>2026-04-05 13:17:02</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:25:39</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:25:44</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:25:47</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:25:50</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:25:53</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:25:56</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:25:59</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:26:02</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:26:06</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:26:10</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:26:14</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:26:48</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:26:53</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:26:56</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:27:00</t>
+  </si>
+  <si>
+    <t>00:00:05</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:35:57</t>
+  </si>
+  <si>
+    <t>00:00:06</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:36:03</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:36:10</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:36:14</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:37:43</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:37:47</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:37:50</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:37:55</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:37:59</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:38:03</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:38:07</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:38:11</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:38:16</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:38:21</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:38:26</t>
+  </si>
+  <si>
+    <t>00:00:35</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:39:02</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:39:07</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:39:11</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:39:16</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:40:54</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:40:58</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:41:01</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:41:04</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:41:52</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:41:55</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:41:58</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:03</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:07</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:14</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:17</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:20</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:24</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:28</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:42:31</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:43:06</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:43:10</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:43:16</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:43:19</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:43:56</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:43:59</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:44:02</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:44:05</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:01</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:05</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:08</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:10</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:14</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:17</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:20</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:23</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:27</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:31</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:52:35</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:53:10</t>
+  </si>
+  <si>
+    <t>00:00:07</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:53:17</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:53:20</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:53:23</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:57:08</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:57:12</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:57:17</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:57:19</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:13</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:16</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:19</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:22</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:25</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:29</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:32</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:35</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:39</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:43</t>
+  </si>
+  <si>
+    <t>2026-04-05 13:59:47</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:00:22</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:00:27</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:00:31</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:00:34</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:03:39</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:03:43</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:03:47</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:03:51</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:06:00</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:06:04</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:06:10</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:06:13</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:26</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:30</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:34</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:38</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:43</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:48</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:53</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:08:58</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:09:03</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:09:09</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:09:15</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:09:50</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:09:56</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:10:00</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:10:04</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:16:14</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:16:19</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:16:23</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:16:26</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:18:25</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:18:30</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:18:33</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:18:37</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:19:42</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:19:46</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:19:49</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:19:55</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:19:59</t>
+  </si>
+  <si>
+    <t>00:00:08</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:20:08</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:20:16</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:20:20</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:20:24</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:20:30</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:20:36</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:21:12</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:21:17</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:21:21</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:21:27</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:27:14</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:27:19</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:29:57</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:33:56</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:34:01</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:34:05</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:34:08</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:11</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:15</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:19</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:23</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:28</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:33</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:37</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:42</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:47</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:53</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:35:59</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:36:35</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:36:41</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:36:44</t>
+  </si>
+  <si>
+    <t>2026-04-05 14:36:48</t>
   </si>
 </sst>
 </file>
@@ -150,7 +642,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="175" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -169,6 +661,960 @@
       <sz val="11.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <color indexed="8"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="58"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -313,7 +1759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -362,6 +1808,483 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="149" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="157" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="159" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="6" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="4" borderId="4" xfId="0" applyFill="true" applyFont="true" applyAlignment="true" applyBorder="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -678,7 +2601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="46.17578125"/>
@@ -958,6 +2881,2709 @@
         <v>40</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s" s="18">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s" s="19">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s" s="20">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s" s="21">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s" s="22">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s" s="23">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s" s="24">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s" s="25">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s" s="26">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s" s="27">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s" s="28">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s" s="29">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s" s="30">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s" s="31">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C31" t="s" s="32">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s" s="33">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s" s="34">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C34" t="s" s="35">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C35" t="s" s="36">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s" s="37">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C37" t="s" s="38">
+        <v>10</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C38" t="s" s="39">
+        <v>6</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C39" t="s" s="40">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C40" t="s" s="41">
+        <v>6</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C41" t="s" s="42">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C42" t="s" s="43">
+        <v>6</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C43" t="s" s="44">
+        <v>6</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C44" t="s" s="45">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E44" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C45" t="s" s="46">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C46" t="s" s="47">
+        <v>10</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C47" t="s" s="48">
+        <v>10</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C48" t="s" s="49">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E48" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C49" t="s" s="50">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s" s="51">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C51" t="s" s="52">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E51" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C52" t="s" s="53">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C53" t="s" s="54">
+        <v>6</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C54" t="s" s="55">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C55" t="s" s="56">
+        <v>6</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C56" t="s" s="57">
+        <v>6</v>
+      </c>
+      <c r="D56" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s" s="0">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C57" t="s" s="58">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C58" t="s" s="59">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E58" t="s" s="0">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C59" t="s" s="60">
+        <v>6</v>
+      </c>
+      <c r="D59" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s" s="0">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C60" t="s" s="61">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E60" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C61" t="s" s="62">
+        <v>6</v>
+      </c>
+      <c r="D61" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s" s="0">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C62" t="s" s="63">
+        <v>6</v>
+      </c>
+      <c r="D62" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C63" t="s" s="64">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s" s="65">
+        <v>6</v>
+      </c>
+      <c r="D64" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E64" t="s" s="0">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C65" t="s" s="66">
+        <v>10</v>
+      </c>
+      <c r="D65" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E65" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C66" t="s" s="67">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E66" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C67" t="s" s="68">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E67" t="s" s="0">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C68" t="s" s="69">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E68" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C69" t="s" s="70">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s" s="0">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C70" t="s" s="71">
+        <v>6</v>
+      </c>
+      <c r="D70" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s" s="72">
+        <v>6</v>
+      </c>
+      <c r="D71" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C72" t="s" s="73">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C73" t="s" s="74">
+        <v>6</v>
+      </c>
+      <c r="D73" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s" s="75">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E74" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C75" t="s" s="76">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E75" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C76" t="s" s="77">
+        <v>6</v>
+      </c>
+      <c r="D76" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C77" t="s" s="78">
+        <v>6</v>
+      </c>
+      <c r="D77" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C78" t="s" s="79">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E78" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C79" t="s" s="80">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E79" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C80" t="s" s="81">
+        <v>6</v>
+      </c>
+      <c r="D80" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E80" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C81" t="s" s="82">
+        <v>6</v>
+      </c>
+      <c r="D81" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E81" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C82" t="s" s="83">
+        <v>6</v>
+      </c>
+      <c r="D82" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E82" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C83" t="s" s="84">
+        <v>6</v>
+      </c>
+      <c r="D83" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E83" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C84" t="s" s="85">
+        <v>10</v>
+      </c>
+      <c r="D84" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E84" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C85" t="s" s="86">
+        <v>10</v>
+      </c>
+      <c r="D85" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E85" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C86" t="s" s="87">
+        <v>6</v>
+      </c>
+      <c r="D86" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="E86" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C87" t="s" s="88">
+        <v>6</v>
+      </c>
+      <c r="D87" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E87" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C88" t="s" s="89">
+        <v>6</v>
+      </c>
+      <c r="D88" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E88" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C89" t="s" s="90">
+        <v>6</v>
+      </c>
+      <c r="D89" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E89" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C90" t="s" s="91">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C91" t="s" s="92">
+        <v>6</v>
+      </c>
+      <c r="D91" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E91" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C92" t="s" s="93">
+        <v>6</v>
+      </c>
+      <c r="D92" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C93" t="s" s="94">
+        <v>6</v>
+      </c>
+      <c r="D93" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E93" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C94" t="s" s="95">
+        <v>6</v>
+      </c>
+      <c r="D94" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E94" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C95" t="s" s="96">
+        <v>6</v>
+      </c>
+      <c r="D95" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E95" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C96" t="s" s="97">
+        <v>6</v>
+      </c>
+      <c r="D96" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E96" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C97" t="s" s="98">
+        <v>6</v>
+      </c>
+      <c r="D97" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E97" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C98" t="s" s="99">
+        <v>6</v>
+      </c>
+      <c r="D98" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E98" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C99" t="s" s="100">
+        <v>6</v>
+      </c>
+      <c r="D99" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E99" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C100" t="s" s="101">
+        <v>6</v>
+      </c>
+      <c r="D100" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E100" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s" s="102">
+        <v>6</v>
+      </c>
+      <c r="D101" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E101" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C102" t="s" s="103">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E102" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C103" t="s" s="104">
+        <v>10</v>
+      </c>
+      <c r="D103" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E103" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C104" t="s" s="105">
+        <v>10</v>
+      </c>
+      <c r="D104" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E104" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C105" t="s" s="106">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E105" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C106" t="s" s="107">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E106" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C107" t="s" s="108">
+        <v>6</v>
+      </c>
+      <c r="D107" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C108" t="s" s="109">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E108" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C109" t="s" s="110">
+        <v>6</v>
+      </c>
+      <c r="D109" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E109" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C110" t="s" s="111">
+        <v>6</v>
+      </c>
+      <c r="D110" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E110" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C111" t="s" s="112">
+        <v>6</v>
+      </c>
+      <c r="D111" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E111" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C112" t="s" s="113">
+        <v>6</v>
+      </c>
+      <c r="D112" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E112" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C113" t="s" s="114">
+        <v>6</v>
+      </c>
+      <c r="D113" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E113" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C114" t="s" s="115">
+        <v>6</v>
+      </c>
+      <c r="D114" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E114" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C115" t="s" s="116">
+        <v>6</v>
+      </c>
+      <c r="D115" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E115" t="s" s="0">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C116" t="s" s="117">
+        <v>6</v>
+      </c>
+      <c r="D116" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E116" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C117" t="s" s="118">
+        <v>6</v>
+      </c>
+      <c r="D117" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E117" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C118" t="s" s="119">
+        <v>6</v>
+      </c>
+      <c r="D118" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E118" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C119" t="s" s="120">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E119" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C120" t="s" s="121">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E120" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C121" t="s" s="122">
+        <v>6</v>
+      </c>
+      <c r="D121" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E121" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C122" t="s" s="123">
+        <v>6</v>
+      </c>
+      <c r="D122" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E122" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C123" t="s" s="124">
+        <v>6</v>
+      </c>
+      <c r="D123" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E123" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B124" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C124" t="s" s="125">
+        <v>6</v>
+      </c>
+      <c r="D124" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E124" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B125" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C125" t="s" s="126">
+        <v>6</v>
+      </c>
+      <c r="D125" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E125" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B126" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C126" t="s" s="127">
+        <v>10</v>
+      </c>
+      <c r="D126" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E126" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B127" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C127" t="s" s="128">
+        <v>10</v>
+      </c>
+      <c r="D127" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E127" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B128" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C128" t="s" s="129">
+        <v>6</v>
+      </c>
+      <c r="D128" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E128" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B129" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C129" t="s" s="130">
+        <v>6</v>
+      </c>
+      <c r="D129" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E129" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B130" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C130" t="s" s="131">
+        <v>6</v>
+      </c>
+      <c r="D130" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E130" t="s" s="0">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B131" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s" s="132">
+        <v>6</v>
+      </c>
+      <c r="D131" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E131" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B132" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C132" t="s" s="133">
+        <v>6</v>
+      </c>
+      <c r="D132" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E132" t="s" s="0">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B133" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C133" t="s" s="134">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E133" t="s" s="0">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C134" t="s" s="135">
+        <v>6</v>
+      </c>
+      <c r="D134" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="E134" t="s" s="0">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B135" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C135" t="s" s="136">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E135" t="s" s="0">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B136" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C136" t="s" s="137">
+        <v>6</v>
+      </c>
+      <c r="D136" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E136" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C137" t="s" s="138">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E137" t="s" s="0">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C138" t="s" s="139">
+        <v>6</v>
+      </c>
+      <c r="D138" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E138" t="s" s="0">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B139" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C139" t="s" s="140">
+        <v>6</v>
+      </c>
+      <c r="D139" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E139" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B140" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C140" t="s" s="141">
+        <v>6</v>
+      </c>
+      <c r="D140" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E140" t="s" s="0">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B141" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C141" t="s" s="142">
+        <v>6</v>
+      </c>
+      <c r="D141" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E141" t="s" s="0">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C142" t="s" s="143">
+        <v>6</v>
+      </c>
+      <c r="D142" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E142" t="s" s="0">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B143" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C143" t="s" s="144">
+        <v>6</v>
+      </c>
+      <c r="D143" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E143" t="s" s="0">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B144" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C144" t="s" s="145">
+        <v>6</v>
+      </c>
+      <c r="D144" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="E144" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B145" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C145" t="s" s="146">
+        <v>6</v>
+      </c>
+      <c r="D145" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="E145" t="s" s="0">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B146" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C146" t="s" s="147">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E146" t="s" s="0">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B147" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C147" t="s" s="148">
+        <v>6</v>
+      </c>
+      <c r="D147" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E147" t="s" s="0">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B148" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C148" t="s" s="149">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E148" t="s" s="0">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B149" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C149" t="s" s="150">
+        <v>10</v>
+      </c>
+      <c r="D149" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E149" t="s" s="0">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B150" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C150" t="s" s="151">
+        <v>10</v>
+      </c>
+      <c r="D150" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E150" t="s" s="0">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B151" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C151" t="s" s="152">
+        <v>6</v>
+      </c>
+      <c r="D151" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E151" t="s" s="0">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B152" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C152" t="s" s="153">
+        <v>6</v>
+      </c>
+      <c r="D152" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E152" t="s" s="0">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B153" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C153" t="s" s="154">
+        <v>6</v>
+      </c>
+      <c r="D153" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E153" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B154" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C154" t="s" s="155">
+        <v>6</v>
+      </c>
+      <c r="D154" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E154" t="s" s="0">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B155" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C155" t="s" s="156">
+        <v>6</v>
+      </c>
+      <c r="D155" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E155" t="s" s="0">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B156" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C156" t="s" s="157">
+        <v>6</v>
+      </c>
+      <c r="D156" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E156" t="s" s="0">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B157" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C157" t="s" s="158">
+        <v>6</v>
+      </c>
+      <c r="D157" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E157" t="s" s="0">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B158" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C158" t="s" s="159">
+        <v>6</v>
+      </c>
+      <c r="D158" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E158" t="s" s="0">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B159" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C159" t="s" s="160">
+        <v>6</v>
+      </c>
+      <c r="D159" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E159" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C160" t="s" s="161">
+        <v>6</v>
+      </c>
+      <c r="D160" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E160" t="s" s="0">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B161" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C161" t="s" s="162">
+        <v>6</v>
+      </c>
+      <c r="D161" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E161" t="s" s="0">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="B162" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C162" t="s" s="163">
+        <v>6</v>
+      </c>
+      <c r="D162" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E162" t="s" s="0">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B163" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C163" t="s" s="164">
+        <v>6</v>
+      </c>
+      <c r="D163" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E163" t="s" s="0">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C164" t="s" s="165">
+        <v>6</v>
+      </c>
+      <c r="D164" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E164" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="B165" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C165" t="s" s="166">
+        <v>6</v>
+      </c>
+      <c r="D165" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E165" t="s" s="0">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B166" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C166" t="s" s="167">
+        <v>6</v>
+      </c>
+      <c r="D166" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E166" t="s" s="0">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="B167" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C167" t="s" s="168">
+        <v>6</v>
+      </c>
+      <c r="D167" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E167" t="s" s="0">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B168" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C168" t="s" s="169">
+        <v>6</v>
+      </c>
+      <c r="D168" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E168" t="s" s="0">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B169" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C169" t="s" s="170">
+        <v>6</v>
+      </c>
+      <c r="D169" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E169" t="s" s="0">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B170" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C170" t="s" s="171">
+        <v>6</v>
+      </c>
+      <c r="D170" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E170" t="s" s="0">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B171" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C171" t="s" s="172">
+        <v>10</v>
+      </c>
+      <c r="D171" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E171" t="s" s="0">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B172" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C172" t="s" s="173">
+        <v>10</v>
+      </c>
+      <c r="D172" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E172" t="s" s="0">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B173" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C173" t="s" s="174">
+        <v>6</v>
+      </c>
+      <c r="D173" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E173" t="s" s="0">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B174" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C174" t="s" s="175">
+        <v>6</v>
+      </c>
+      <c r="D174" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E174" t="s" s="0">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B175" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C175" t="s" s="176">
+        <v>6</v>
+      </c>
+      <c r="D175" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E175" t="s" s="0">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
